--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -2,41 +2,57 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="50600" yWindow="6420" windowWidth="102400" windowHeight="28180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生データ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="説明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -48,14 +64,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00667eea"/>
-        <bgColor rgb="00667eea"/>
+        <fgColor rgb="FF667EEA"/>
+        <bgColor rgb="FF667EEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="FFE0E0E0"/>
+        <bgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +102,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -450,17 +466,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="85.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -534,10 +547,26 @@
           <t>AI IWAFUNE</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>魔法少女キャラクターを規定する武器表現の研究</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>image16.png,image18.png,image11.jpeg,image1.jpg,image15.jpg</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>1522008.pdf</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>1522008.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -563,10 +592,21 @@
           <t>MIZUKI OTSUKA</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>AIを用いたキャラクターの簡便な3D化手法とデザイン保持の研究</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>1522012.pdf</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>1522012.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -592,10 +632,26 @@
           <t>NATSUHA ONISHI</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Vtuberのキャラクター属性を空間デザイン要素へ翻訳するための手法の研究―星川サラを例にして</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>image10.png,image1.png,image24.png,image37.png,image44.png</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>1522014.pdf</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>1522014.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -621,10 +677,26 @@
           <t>HINA KOMORI</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>「Live2Dを前提としたキャラクターデザイン手法の研究</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>image7.png,image3.png,image1.png,image4.png,image5.png</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>1522030.pdf</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>1522030.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -650,10 +722,26 @@
           <t>MEI SAKAGUCHI</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>総合芸術としての個人ゲーム制作―『残響旧街路』の世界観構築を中心に</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>image5.png,image17.jpg,image11.jpg,image18.jpg,image6.jpg</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1522034.pdf</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>1522034.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -679,10 +767,26 @@
           <t>KOHAKU SHIKATA</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>『もちこの大冒険』ーピクセルアートによるアクションゲーム表現の研究ー</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>image3.png,image14.png,image10.png,image4.png,image2.gif</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>1522036.pdf</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>1522036.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -708,10 +812,26 @@
           <t>MINA TAKAHASHI</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ノベル形式ホラーゲームにおけるキャラクター関係性の揺らぎと、恋愛要素がもたらす機能</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>image3.jpg,image9.png,image2.jpg,image12.png,image13.png</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1522047.pdf</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>1522047.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -737,10 +857,26 @@
           <t>KIIKA NISHIZAWA</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>合成音声キャラクターの声と物語体験：ノベルゲーム制作による表現と解釈の深化</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>image14.jpg,image4.png,image11.jpg,image8.png,image9.jpg</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>1522054.pdf</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>1522054.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -766,13 +902,30 @@
           <t>NAO YAMAMOTO</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>自己キャラクター化の実践を通じて捉えるVtuber文化</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>image5.png,image1.png,image23.png,image38.png,image24.png</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>1522074.pdf</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>1522074.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -783,38 +936,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Excelファイル項目説明</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr"/>
-      <c r="C1" s="4" t="inlineStr"/>
-      <c r="D1" s="4" t="inlineStr"/>
-      <c r="E1" s="4" t="inlineStr"/>
-      <c r="F1" s="4" t="inlineStr"/>
-      <c r="G1" s="4" t="inlineStr"/>
-      <c r="H1" s="4" t="inlineStr"/>
-      <c r="I1" s="4" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -832,12 +973,12 @@
           <t>例</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -855,12 +996,6 @@
           <t>1, 2, 3...</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -878,12 +1013,6 @@
           <t>メデ4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -901,12 +1030,6 @@
           <t>1522008</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -924,12 +1047,6 @@
           <t>岩舩　愛</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -947,12 +1064,6 @@
           <t>AI IWAFUNE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -970,12 +1081,6 @@
           <t>AIを活用した画像認識システムの開発</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,12 +1098,6 @@
           <t>image1.jpg または image1.jpg,image2.jpg</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1016,12 +1115,6 @@
           <t>report.docx または report1.docx,report2.docx</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1039,23 +1132,6 @@
           <t>presentation.pptx または pres1.pptx,pres2.pptx</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1063,14 +1139,6 @@
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1078,14 +1146,6 @@
           <t>1. ファイル名に日本語や特殊文字を含めないことを推奨します</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1093,14 +1153,6 @@
           <t>2. 画像ファイルは assets/images/ フォルダに配置してください</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1108,14 +1160,6 @@
           <t>3. レポートファイルは assets/reports/ フォルダに配置してください</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1123,14 +1167,6 @@
           <t>4. プレゼン資料ファイルは assets/presentations/ フォルダに配置してください</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1138,14 +1174,6 @@
           <t>5. 複数のファイルを指定する場合は、カンマ区切りで入力してください</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="50600" yWindow="6420" windowWidth="102400" windowHeight="28180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="34680" yWindow="6400" windowWidth="42320" windowHeight="28180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生データ" sheetId="1" state="visible" r:id="rId1"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -522,6 +522,11 @@
           <t>プレゼンパス</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>キーワード</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -554,7 +559,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>image16.png,image18.png,image11.jpeg,image1.jpg,image15.jpg</t>
+          <t>image6.png</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -565,6 +570,11 @@
       <c r="I2" s="3" t="inlineStr">
         <is>
           <t>1522008.pdf</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>デジタルファブリケーション, スペキュラティブデザイン, マンガ・アニメ, Blender</t>
         </is>
       </c>
     </row>
@@ -597,14 +607,16 @@
           <t>AIを用いたキャラクターの簡便な3D化手法とデザイン保持の研究</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1522012.pdf</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>1522012.pdf</t>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AIモデリング, 3Dモデリング, キャラクターデザイン, デザイン技法</t>
         </is>
       </c>
     </row>
@@ -639,7 +651,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>image10.png,image1.png,image24.png,image37.png,image44.png</t>
+          <t>image37.png</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -650,6 +662,11 @@
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>1522014.pdf</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3Dモデリング, VTuber, ペルソナ分析, Blender, ファンアート, 空間デザイン</t>
         </is>
       </c>
     </row>
@@ -684,7 +701,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>image7.png,image3.png,image1.png,image4.png,image5.png</t>
+          <t>image6.png</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -695,6 +712,11 @@
       <c r="I5" s="3" t="inlineStr">
         <is>
           <t>1522030.pdf</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Live2D, キャラクターデザイン</t>
         </is>
       </c>
     </row>
@@ -729,7 +751,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>image5.png,image17.jpg,image11.jpg,image18.jpg,image6.jpg</t>
+          <t>image17.jpg</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -740,6 +762,11 @@
       <c r="I6" s="3" t="inlineStr">
         <is>
           <t>1522034.pdf</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ゲーム開発, Unity, アドベンチャーゲーム, UIデザイン</t>
         </is>
       </c>
     </row>
@@ -774,7 +801,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>image3.png,image14.png,image10.png,image4.png,image2.gif</t>
+          <t>image2.gif</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -785,6 +812,11 @@
       <c r="I7" s="3" t="inlineStr">
         <is>
           <t>1522036.pdf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ゲーム開発, Unity, アクションゲーム, 体験のデザイン</t>
         </is>
       </c>
     </row>
@@ -819,7 +851,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>image3.jpg,image9.png,image2.jpg,image12.png,image13.png</t>
+          <t>image8.jpg</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -830,6 +862,11 @@
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>1522047.pdf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ティラノビルダー, ノベルゲーム, イラスト</t>
         </is>
       </c>
     </row>
@@ -864,7 +901,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>image14.jpg,image4.png,image11.jpg,image8.png,image9.jpg</t>
+          <t>image11.jpg</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -875,6 +912,11 @@
       <c r="I9" s="3" t="inlineStr">
         <is>
           <t>1522054.pdf</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ティラノビルダー, ノベルゲーム, 音声合成, シナリオ</t>
         </is>
       </c>
     </row>
@@ -909,7 +951,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>image5.png,image1.png,image23.png,image38.png,image24.png</t>
+          <t>image24.png</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -920,6 +962,11 @@
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t>1522074.pdf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Vtuber, Live配信, 〜〜研究</t>
         </is>
       </c>
     </row>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="34680" yWindow="6400" windowWidth="42320" windowHeight="28180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="48160" yWindow="620" windowWidth="42320" windowHeight="28180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生データ" sheetId="1" state="visible" r:id="rId1"/>
@@ -465,15 +465,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="4.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10" bestFit="1" customWidth="1" min="2" max="3"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="85.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="9"/>
+    <col width="9.83203125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="13" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="66.33203125" bestFit="1" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -559,7 +562,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>image6.png</t>
+          <t>image1.png,image10.png,image11.png,image12.png,image13.png,image14.png,image15.png,image16.png,image18.png,image19.png</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -607,7 +610,6 @@
           <t>AIを用いたキャラクターの簡便な3D化手法とデザイン保持の研究</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1522012.pdf</t>
@@ -651,7 +653,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>image37.png</t>
+          <t>image1.png,image10.png,image12.png,image14.svg,image16.svg,image18.svg,image2.png,image20.svg,image22.svg,image24.png</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -701,7 +703,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>image6.png</t>
+          <t>image1.png,image2.png,image3.png,image4.png,image5.png,image6.png,image7.png,image8.png</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -751,7 +753,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>image17.jpg</t>
+          <t>image1.png,image11.png,image16.png,image17.png,image18.png,image19.png,image2.png,image20.png,image21.png,image24.png</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -801,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>image2.gif</t>
+          <t>image1.png,image10.png,image13.png,image14.png,image15.png,image2.png,image3.png,image4.png,image5.png,image6.png</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -851,7 +853,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>image8.jpg</t>
+          <t>image1.png,image10.png,image11.png,image12.png,image13.png,image14.png,image2.png,image3.png,image4.png,image5.png</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -901,7 +903,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>image11.jpg</t>
+          <t>image1.png,image11.png,image12.png,image13.png,image14.png,image3.png,image4.png,image5.png,image7.png,image8.png</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -951,10 +953,10 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>image24.png</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+          <t>image1.png,image10.png,image11.svg,image12.png,image13.png,image14.svg,image17.svg,image2.png,image23.png,image24.png</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>1522074.pdf</t>
         </is>
@@ -966,9 +968,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Vtuber, Live配信, 〜〜研究</t>
-        </is>
-      </c>
+          <t>Vtuber, Live配信, 文化研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/takawo/Library/CloudStorage/Dropbox/260126卒業研究発表_資料ウェブサイト/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D2A388-D9BD-4D4B-8025-5E40EBED4489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C178E8F-6F8A-774F-B849-9F346BBA5CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18580" yWindow="620" windowWidth="42320" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57800" yWindow="1140" windowWidth="42320" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="学生データ" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="104">
   <si>
     <t>No</t>
   </si>
@@ -290,9 +290,6 @@
     <t>image6.png</t>
   </si>
   <si>
-    <t>image37.png</t>
-  </si>
-  <si>
     <t>image17.png</t>
   </si>
   <si>
@@ -306,6 +303,40 @@
   </si>
   <si>
     <t>image24.png</t>
+  </si>
+  <si>
+    <t>hero動画</t>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ドウガ </t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>1522008.mp4</t>
+  </si>
+  <si>
+    <t>1522014.mp4</t>
+  </si>
+  <si>
+    <t>1522030.mp4</t>
+  </si>
+  <si>
+    <t>1522034.mp4</t>
+  </si>
+  <si>
+    <t>1522036.mp4</t>
+  </si>
+  <si>
+    <t>1522054.mp4</t>
+  </si>
+  <si>
+    <t>1522074.mp4</t>
+  </si>
+  <si>
+    <t>image7.png</t>
+  </si>
+  <si>
+    <t>image42.png</t>
   </si>
 </sst>
 </file>
@@ -697,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -705,13 +736,14 @@
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="85.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="106.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="66.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="66.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25" customHeight="1">
+    <row r="1" spans="1:11" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -740,15 +772,18 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
+      <c r="B2" s="3">
+        <v>2025</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>11</v>
@@ -772,15 +807,18 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
+      <c r="B3" s="3">
+        <v>2025</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>17</v>
@@ -794,20 +832,26 @@
       <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
+      <c r="B4" s="3">
+        <v>2025</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>23</v>
@@ -822,7 +866,7 @@
         <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>27</v>
@@ -831,15 +875,18 @@
         <v>27</v>
       </c>
       <c r="J4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
+      <c r="B5" s="3">
+        <v>2025</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>29</v>
@@ -863,15 +910,18 @@
         <v>33</v>
       </c>
       <c r="J5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
+      <c r="B6" s="3">
+        <v>2025</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>35</v>
@@ -886,7 +936,7 @@
         <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>39</v>
@@ -895,15 +945,18 @@
         <v>39</v>
       </c>
       <c r="J6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
+      <c r="B7" s="3">
+        <v>2025</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>41</v>
@@ -918,7 +971,7 @@
         <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>45</v>
@@ -927,15 +980,18 @@
         <v>45</v>
       </c>
       <c r="J7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
+      <c r="B8" s="3">
+        <v>2025</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>47</v>
@@ -950,7 +1006,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>51</v>
@@ -958,16 +1014,16 @@
       <c r="I8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
+      <c r="B9" s="3">
+        <v>2025</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>53</v>
@@ -982,7 +1038,7 @@
         <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>57</v>
@@ -991,15 +1047,18 @@
         <v>57</v>
       </c>
       <c r="J9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
+      <c r="B10" s="3">
+        <v>2025</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>59</v>
@@ -1014,7 +1073,7 @@
         <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s">
         <v>63</v>
@@ -1023,10 +1082,13 @@
         <v>63</v>
       </c>
       <c r="J10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="H11" s="3"/>
     </row>
   </sheetData>
